--- a/results/phi4_14b/comparison_ToTPlainLLM/ToTPlainLLM_costs.xlsx
+++ b/results/phi4_14b/comparison_ToTPlainLLM/ToTPlainLLM_costs.xlsx
@@ -472,10 +472,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94.72086834907532</v>
+        <v>357.4797494411469</v>
       </c>
       <c r="B2" t="n">
-        <v>1122.65234375</v>
+        <v>1141.3203125</v>
       </c>
       <c r="C2" t="n">
         <v>11.2</v>
@@ -490,7 +490,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>94.72086501121521</v>
+        <v>357.4797463417053</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -498,13 +498,13 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>78.69850206375122</v>
+        <v>112.5541603565216</v>
       </c>
       <c r="B3" t="n">
-        <v>1122.6640625</v>
+        <v>1141.3203125</v>
       </c>
       <c r="C3" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="D3" t="n">
         <v>20</v>
@@ -516,7 +516,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>78.69849872589111</v>
+        <v>112.5541582107544</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -524,13 +524,13 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86.75945425033569</v>
+        <v>76.23814964294434</v>
       </c>
       <c r="B4" t="n">
-        <v>1122.6640625</v>
+        <v>1141.3203125</v>
       </c>
       <c r="C4" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="D4" t="n">
         <v>20</v>
@@ -542,7 +542,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>86.7594518661499</v>
+        <v>76.2381477355957</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -550,13 +550,13 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>84.11814975738525</v>
+        <v>107.1122486591339</v>
       </c>
       <c r="B5" t="n">
-        <v>1122.67578125</v>
+        <v>1142.5625</v>
       </c>
       <c r="C5" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="D5" t="n">
         <v>20</v>
@@ -568,7 +568,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>84.11814785003662</v>
+        <v>107.1122469902039</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -576,13 +576,13 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88.79808306694031</v>
+        <v>144.3680624961853</v>
       </c>
       <c r="B6" t="n">
-        <v>1122.6953125</v>
+        <v>1142.59375</v>
       </c>
       <c r="C6" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="D6" t="n">
         <v>20</v>
@@ -594,7 +594,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>88.7980809211731</v>
+        <v>144.3680603504181</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -602,10 +602,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>190.122665643692</v>
+        <v>163.4634017944336</v>
       </c>
       <c r="B7" t="n">
-        <v>1123.3828125</v>
+        <v>1143.15234375</v>
       </c>
       <c r="C7" t="n">
         <v>11.2</v>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>190.122663974762</v>
+        <v>163.4633996486664</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -628,16 +628,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1839.618708848953</v>
+        <v>136.2415952682495</v>
       </c>
       <c r="B8" t="n">
-        <v>1123.3828125</v>
+        <v>1143.15234375</v>
       </c>
       <c r="C8" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1839.618706464767</v>
+        <v>136.2415935993195</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -654,16 +654,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.004527091979980469</v>
+        <v>145.3399896621704</v>
       </c>
       <c r="B9" t="n">
-        <v>1123.390625</v>
+        <v>1143.15625</v>
       </c>
       <c r="C9" t="n">
-        <v>14.3</v>
+        <v>11.2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004525184631347656</v>
+        <v>145.3399877548218</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.005049228668212891</v>
+        <v>136.2519607543945</v>
       </c>
       <c r="B10" t="n">
-        <v>1123.390625</v>
+        <v>1143.15625</v>
       </c>
       <c r="C10" t="n">
-        <v>28.6</v>
+        <v>11.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005048036575317383</v>
+        <v>136.2519583702087</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -706,16 +706,16 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.004726171493530273</v>
+        <v>152.481627702713</v>
       </c>
       <c r="B11" t="n">
-        <v>1123.390625</v>
+        <v>1143.15625</v>
       </c>
       <c r="C11" t="n">
-        <v>28.6</v>
+        <v>11.2</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -724,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.004724979400634766</v>
+        <v>152.4816253185272</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -732,16 +732,16 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.005066871643066406</v>
+        <v>141.4631941318512</v>
       </c>
       <c r="B12" t="n">
-        <v>1123.390625</v>
+        <v>1143.15625</v>
       </c>
       <c r="C12" t="n">
-        <v>14.3</v>
+        <v>11.3</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005065679550170898</v>
+        <v>141.4631922245026</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -758,16 +758,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.004384517669677734</v>
+        <v>137.0116283893585</v>
       </c>
       <c r="B13" t="n">
-        <v>1123.39453125</v>
+        <v>1143.15625</v>
       </c>
       <c r="C13" t="n">
-        <v>16.7</v>
+        <v>11.3</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -776,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004383325576782227</v>
+        <v>137.0116257667542</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -784,16 +784,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.005068302154541016</v>
+        <v>144.6424534320831</v>
       </c>
       <c r="B14" t="n">
-        <v>1123.39453125</v>
+        <v>1143.15625</v>
       </c>
       <c r="C14" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.005066871643066406</v>
+        <v>144.6424515247345</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -810,16 +810,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.00436854362487793</v>
+        <v>104.5464208126068</v>
       </c>
       <c r="B15" t="n">
-        <v>1123.39453125</v>
+        <v>1143.15625</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.004367351531982422</v>
+        <v>104.5464189052582</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -836,16 +836,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.005170822143554688</v>
+        <v>84.60864543914795</v>
       </c>
       <c r="B16" t="n">
-        <v>1123.40234375</v>
+        <v>1143.15625</v>
       </c>
       <c r="C16" t="n">
-        <v>28.6</v>
+        <v>11.3</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -854,7 +854,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.005169868469238281</v>
+        <v>84.60864305496216</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,16 +862,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.005335807800292969</v>
+        <v>260.9812581539154</v>
       </c>
       <c r="B17" t="n">
-        <v>1123.40234375</v>
+        <v>1143.45703125</v>
       </c>
       <c r="C17" t="n">
-        <v>14.3</v>
+        <v>11.2</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.005334377288818359</v>
+        <v>260.9812557697296</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.004564285278320312</v>
+        <v>134.8547093868256</v>
       </c>
       <c r="B18" t="n">
-        <v>1123.40234375</v>
+        <v>1143.45703125</v>
       </c>
       <c r="C18" t="n">
-        <v>28.6</v>
+        <v>11.1</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.004563093185424805</v>
+        <v>134.8547077178955</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -914,16 +914,16 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.004685640335083008</v>
+        <v>226.1297030448914</v>
       </c>
       <c r="B19" t="n">
-        <v>1123.40234375</v>
+        <v>1143.45703125</v>
       </c>
       <c r="C19" t="n">
-        <v>16.7</v>
+        <v>11.2</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0046844482421875</v>
+        <v>226.1297013759613</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -940,16 +940,16 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.004860639572143555</v>
+        <v>107.4050352573395</v>
       </c>
       <c r="B20" t="n">
-        <v>1123.40234375</v>
+        <v>1143.45703125</v>
       </c>
       <c r="C20" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.004859209060668945</v>
+        <v>107.4050335884094</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -966,16 +966,16 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.006316423416137695</v>
+        <v>247.9082510471344</v>
       </c>
       <c r="B21" t="n">
-        <v>1123.40234375</v>
+        <v>1143.83984375</v>
       </c>
       <c r="C21" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -984,7 +984,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.006315231323242188</v>
+        <v>247.9082491397858</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -992,16 +992,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.005105257034301758</v>
+        <v>117.3308753967285</v>
       </c>
       <c r="B22" t="n">
-        <v>1123.40234375</v>
+        <v>1143.83984375</v>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>11.2</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1010,7 +1010,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.005104303359985352</v>
+        <v>117.3308732509613</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.00477910041809082</v>
+        <v>124.5384719371796</v>
       </c>
       <c r="B23" t="n">
-        <v>1123.40234375</v>
+        <v>1143.83984375</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.004777669906616211</v>
+        <v>124.5384700298309</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1044,16 +1044,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.004363298416137695</v>
+        <v>95.00139808654785</v>
       </c>
       <c r="B24" t="n">
-        <v>1123.40234375</v>
+        <v>1143.83984375</v>
       </c>
       <c r="C24" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.004362106323242188</v>
+        <v>95.00139617919922</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1070,16 +1070,16 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.004282951354980469</v>
+        <v>91.19555759429932</v>
       </c>
       <c r="B25" t="n">
-        <v>1123.40234375</v>
+        <v>1143.83984375</v>
       </c>
       <c r="C25" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.004281997680664062</v>
+        <v>91.19555568695068</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1096,16 +1096,16 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.004305124282836914</v>
+        <v>106.1392505168915</v>
       </c>
       <c r="B26" t="n">
-        <v>1123.40234375</v>
+        <v>1143.83984375</v>
       </c>
       <c r="C26" t="n">
-        <v>28.6</v>
+        <v>11.2</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.004303932189941406</v>
+        <v>106.1392481327057</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1122,16 +1122,16 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.004641532897949219</v>
+        <v>103.4501783847809</v>
       </c>
       <c r="B27" t="n">
-        <v>1123.40234375</v>
+        <v>1143.83984375</v>
       </c>
       <c r="C27" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.004640340805053711</v>
+        <v>103.4501767158508</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1148,16 +1148,16 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.004210948944091797</v>
+        <v>84.53739094734192</v>
       </c>
       <c r="B28" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C28" t="n">
-        <v>16.7</v>
+        <v>10.9</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.004209518432617188</v>
+        <v>84.53738880157471</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.004166364669799805</v>
+        <v>93.31278967857361</v>
       </c>
       <c r="B29" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C29" t="n">
-        <v>20</v>
+        <v>11.2</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1192,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004165172576904297</v>
+        <v>93.31278657913208</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1200,16 +1200,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.004261255264282227</v>
+        <v>98.98690176010132</v>
       </c>
       <c r="B30" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C30" t="n">
-        <v>16.7</v>
+        <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00426030158996582</v>
+        <v>98.98690009117126</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1226,16 +1226,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.00490880012512207</v>
+        <v>105.6402773857117</v>
       </c>
       <c r="B31" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C31" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.004907369613647461</v>
+        <v>105.6402752399445</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1252,16 +1252,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.004701137542724609</v>
+        <v>124.7044413089752</v>
       </c>
       <c r="B32" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C32" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.00469970703125</v>
+        <v>124.704439163208</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1278,16 +1278,16 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.005225896835327148</v>
+        <v>127.8965017795563</v>
       </c>
       <c r="B33" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C33" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.005224466323852539</v>
+        <v>127.8964996337891</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1304,16 +1304,16 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.004812240600585938</v>
+        <v>142.8077058792114</v>
       </c>
       <c r="B34" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C34" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.004810810089111328</v>
+        <v>142.8077032566071</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1330,16 +1330,16 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.004779338836669922</v>
+        <v>165.5424296855927</v>
       </c>
       <c r="B35" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C35" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.004778146743774414</v>
+        <v>165.542427778244</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1356,16 +1356,16 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.004572391510009766</v>
+        <v>76.21960973739624</v>
       </c>
       <c r="B36" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C36" t="n">
-        <v>28.6</v>
+        <v>11.2</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.004571199417114258</v>
+        <v>76.21960830688477</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.004868984222412109</v>
+        <v>154.8029301166534</v>
       </c>
       <c r="B37" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -1400,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0048675537109375</v>
+        <v>154.8029284477234</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1408,16 +1408,16 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.005226612091064453</v>
+        <v>147.9729285240173</v>
       </c>
       <c r="B38" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C38" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -1426,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.005225419998168945</v>
+        <v>147.9729256629944</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.004976511001586914</v>
+        <v>119.3711941242218</v>
       </c>
       <c r="B39" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C39" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.004974842071533203</v>
+        <v>119.3711924552917</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1460,16 +1460,16 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.004554986953735352</v>
+        <v>69.96300411224365</v>
       </c>
       <c r="B40" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C40" t="n">
-        <v>28.6</v>
+        <v>11</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.004553318023681641</v>
+        <v>69.9630024433136</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1486,16 +1486,16 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.004565954208374023</v>
+        <v>95.63628792762756</v>
       </c>
       <c r="B41" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C41" t="n">
-        <v>16.7</v>
+        <v>11.2</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1504,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.004564285278320312</v>
+        <v>95.63628602027893</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.004625558853149414</v>
+        <v>120.2786238193512</v>
       </c>
       <c r="B42" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C42" t="n">
-        <v>14.3</v>
+        <v>11</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.004624366760253906</v>
+        <v>120.2786219120026</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1538,16 +1538,16 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.004966259002685547</v>
+        <v>106.8822479248047</v>
       </c>
       <c r="B43" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C43" t="n">
-        <v>16.7</v>
+        <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -1556,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.004964590072631836</v>
+        <v>106.8822462558746</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1564,16 +1564,16 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.004804134368896484</v>
+        <v>157.1842715740204</v>
       </c>
       <c r="B44" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C44" t="n">
-        <v>14.3</v>
+        <v>11.2</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -1582,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.004802942276000977</v>
+        <v>157.1842694282532</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1590,16 +1590,16 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.02427864074707031</v>
+        <v>138.9182333946228</v>
       </c>
       <c r="B45" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C45" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -1608,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0242767333984375</v>
+        <v>138.9182312488556</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1616,16 +1616,16 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.006393671035766602</v>
+        <v>180.024760723114</v>
       </c>
       <c r="B46" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C46" t="n">
-        <v>33.3</v>
+        <v>11.1</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -1634,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.006392240524291992</v>
+        <v>180.0247592926025</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1642,16 +1642,16 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.004973411560058594</v>
+        <v>113.5959522724152</v>
       </c>
       <c r="B47" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C47" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -1660,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.004972219467163086</v>
+        <v>113.5959503650665</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1668,16 +1668,16 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.004350423812866211</v>
+        <v>117.8152034282684</v>
       </c>
       <c r="B48" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C48" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -1686,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.004349470138549805</v>
+        <v>117.8152012825012</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.004386425018310547</v>
+        <v>147.8670449256897</v>
       </c>
       <c r="B49" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C49" t="n">
-        <v>20</v>
+        <v>11.2</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.004385471343994141</v>
+        <v>147.8670434951782</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1720,16 +1720,16 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.004369020462036133</v>
+        <v>106.4883341789246</v>
       </c>
       <c r="B50" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C50" t="n">
-        <v>28.6</v>
+        <v>11</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.004368066787719727</v>
+        <v>106.4883320331573</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1746,16 +1746,16 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.004922151565551758</v>
+        <v>172.8681766986847</v>
       </c>
       <c r="B51" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C51" t="n">
-        <v>14.3</v>
+        <v>11.2</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.004920721054077148</v>
+        <v>172.8681747913361</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.005550146102905273</v>
+        <v>118.1838927268982</v>
       </c>
       <c r="B52" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C52" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.005548954010009766</v>
+        <v>118.1838910579681</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1798,16 +1798,16 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.005043745040893555</v>
+        <v>148.6964213848114</v>
       </c>
       <c r="B53" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.005042314529418945</v>
+        <v>148.6964192390442</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1824,16 +1824,16 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.004662036895751953</v>
+        <v>165.4327266216278</v>
       </c>
       <c r="B54" t="n">
-        <v>1123.40234375</v>
+        <v>1143.84375</v>
       </c>
       <c r="C54" t="n">
-        <v>16.7</v>
+        <v>11.2</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.004660844802856445</v>
+        <v>165.4327247142792</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1850,16 +1850,16 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.004498004913330078</v>
+        <v>108.4078235626221</v>
       </c>
       <c r="B55" t="n">
-        <v>1123.40625</v>
+        <v>1143.84375</v>
       </c>
       <c r="C55" t="n">
-        <v>16.7</v>
+        <v>11.3</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.004496574401855469</v>
+        <v>108.4078204631805</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1876,16 +1876,16 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.004472494125366211</v>
+        <v>167.2111263275146</v>
       </c>
       <c r="B56" t="n">
-        <v>1123.40625</v>
+        <v>1143.84375</v>
       </c>
       <c r="C56" t="n">
-        <v>28.6</v>
+        <v>11.1</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.004471302032470703</v>
+        <v>167.2111239433289</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -1902,16 +1902,16 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.005785703659057617</v>
+        <v>125.3412051200867</v>
       </c>
       <c r="B57" t="n">
-        <v>1123.40625</v>
+        <v>1143.84375</v>
       </c>
       <c r="C57" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.005784273147583008</v>
+        <v>125.3412027359009</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -1928,16 +1928,16 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.004800796508789062</v>
+        <v>123.655928850174</v>
       </c>
       <c r="B58" t="n">
-        <v>1123.40625</v>
+        <v>1143.84375</v>
       </c>
       <c r="C58" t="n">
-        <v>16.7</v>
+        <v>11.2</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.004799604415893555</v>
+        <v>123.6559269428253</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.004457712173461914</v>
+        <v>236.043247461319</v>
       </c>
       <c r="B59" t="n">
-        <v>1123.40625</v>
+        <v>1143.84375</v>
       </c>
       <c r="C59" t="n">
-        <v>16.7</v>
+        <v>11</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -1972,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.004456520080566406</v>
+        <v>236.0432453155518</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -1980,16 +1980,16 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.004843473434448242</v>
+        <v>144.837372303009</v>
       </c>
       <c r="B60" t="n">
-        <v>1123.40625</v>
+        <v>1143.84375</v>
       </c>
       <c r="C60" t="n">
-        <v>8.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.004842042922973633</v>
+        <v>144.8373699188232</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2006,16 +2006,16 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.004336833953857422</v>
+        <v>131.7944266796112</v>
       </c>
       <c r="B61" t="n">
-        <v>1123.40625</v>
+        <v>1143.84375</v>
       </c>
       <c r="C61" t="n">
-        <v>28.6</v>
+        <v>11.1</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -2024,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.004335403442382812</v>
+        <v>131.7944247722626</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2032,16 +2032,16 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.004203557968139648</v>
+        <v>111.8854613304138</v>
       </c>
       <c r="B62" t="n">
-        <v>1123.40625</v>
+        <v>1143.84375</v>
       </c>
       <c r="C62" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.004202604293823242</v>
+        <v>111.8854596614838</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2058,16 +2058,16 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.00434112548828125</v>
+        <v>106.5428774356842</v>
       </c>
       <c r="B63" t="n">
-        <v>1123.40625</v>
+        <v>1143.84375</v>
       </c>
       <c r="C63" t="n">
-        <v>16.7</v>
+        <v>11.2</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0.004340171813964844</v>
+        <v>106.5428755283356</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2084,16 +2084,16 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.004912137985229492</v>
+        <v>112.4888696670532</v>
       </c>
       <c r="B64" t="n">
-        <v>1123.40625</v>
+        <v>1143.84375</v>
       </c>
       <c r="C64" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.004910945892333984</v>
+        <v>112.4888679981232</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2110,16 +2110,16 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.004820346832275391</v>
+        <v>80.99205613136292</v>
       </c>
       <c r="B65" t="n">
-        <v>1123.40625</v>
+        <v>1143.84375</v>
       </c>
       <c r="C65" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.004818916320800781</v>
+        <v>80.99205470085144</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.004858732223510742</v>
+        <v>166.804878950119</v>
       </c>
       <c r="B66" t="n">
-        <v>1123.40625</v>
+        <v>1143.84375</v>
       </c>
       <c r="C66" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.004857540130615234</v>
+        <v>166.8048768043518</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2162,16 +2162,16 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.004599094390869141</v>
+        <v>109.775824546814</v>
       </c>
       <c r="B67" t="n">
-        <v>1123.40625</v>
+        <v>1143.84375</v>
       </c>
       <c r="C67" t="n">
-        <v>16.7</v>
+        <v>11</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.004597663879394531</v>
+        <v>109.7758226394653</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2188,16 +2188,16 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.005398750305175781</v>
+        <v>96.68934273719788</v>
       </c>
       <c r="B68" t="n">
-        <v>1123.40625</v>
+        <v>1143.84375</v>
       </c>
       <c r="C68" t="n">
-        <v>14.3</v>
+        <v>11.2</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -2206,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.005397319793701172</v>
+        <v>96.68934011459351</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
